--- a/diseases/d013/2026-2029.xlsx
+++ b/diseases/d013/2026-2029.xlsx
@@ -1998,7 +1998,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11394,7 +11394,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14392,7 +14392,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15782,7 +15782,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16988,7 +16988,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18082,7 +18082,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -18484,7 +18484,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -18886,7 +18886,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19288,7 +19288,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">

--- a/diseases/d013/2026-2029.xlsx
+++ b/diseases/d013/2026-2029.xlsx
@@ -1998,7 +1998,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11394,7 +11394,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14392,7 +14392,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15782,7 +15782,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16988,7 +16988,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18082,7 +18082,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -18484,7 +18484,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -18886,7 +18886,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19288,7 +19288,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">

--- a/diseases/d013/2026-2029.xlsx
+++ b/diseases/d013/2026-2029.xlsx
@@ -19669,6 +19669,408 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN105" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19702,7 +20104,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -19785,7 +20187,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10">
@@ -19795,7 +20197,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11">
@@ -19815,7 +20217,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d013/2026-2029.xlsx
+++ b/diseases/d013/2026-2029.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1209,9 +1206,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1357,9 +1351,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1756,9 +1747,6 @@
       <c r="P8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2008,7 +1996,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2158,9 +2146,6 @@
       <c r="P10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2410,7 +2395,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2560,9 +2545,6 @@
       <c r="P12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -2812,7 +2794,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -2962,9 +2944,6 @@
       <c r="P14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3214,7 +3193,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3657,9 +3636,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -3808,9 +3784,6 @@
       <c r="P19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -4060,7 +4033,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN20" t="b">
@@ -4207,9 +4180,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4355,9 +4325,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4754,9 +4721,6 @@
       <c r="P24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -5006,7 +4970,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5156,9 +5120,6 @@
       <c r="P26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5408,7 +5369,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -5558,9 +5519,6 @@
       <c r="P28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -5810,7 +5768,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6253,9 +6211,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -6404,9 +6359,6 @@
       <c r="P33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -6656,7 +6608,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -6803,9 +6755,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -6951,9 +6900,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -7350,9 +7296,6 @@
       <c r="P38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -7602,7 +7545,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -7752,9 +7695,6 @@
       <c r="P40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -8004,7 +7944,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8154,9 +8094,6 @@
       <c r="P42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -8406,7 +8343,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -8556,9 +8493,6 @@
       <c r="P44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -8808,7 +8742,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -8955,9 +8889,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -9251,9 +9182,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -9399,9 +9327,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -9547,9 +9472,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -9946,9 +9868,6 @@
       <c r="P52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -10198,7 +10117,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -10348,9 +10267,6 @@
       <c r="P54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -10600,7 +10516,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -10750,9 +10666,6 @@
       <c r="P56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -11002,7 +10915,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -11152,9 +11065,6 @@
       <c r="P58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -11404,7 +11314,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -11551,9 +11461,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -11847,9 +11754,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -11995,9 +11899,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -12143,9 +12044,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -12542,9 +12440,6 @@
       <c r="P66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -12794,7 +12689,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -12944,9 +12839,6 @@
       <c r="P68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -13196,7 +13088,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -13346,9 +13238,6 @@
       <c r="P70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -13598,7 +13487,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -13748,9 +13637,6 @@
       <c r="P72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -14000,7 +13886,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -14150,9 +14036,6 @@
       <c r="P74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -14402,7 +14285,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -14549,9 +14432,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -14845,9 +14725,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -14993,9 +14870,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -15141,9 +15015,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -15540,9 +15411,6 @@
       <c r="P82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -15792,7 +15660,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -15942,9 +15810,6 @@
       <c r="P84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -16194,7 +16059,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -16344,9 +16209,6 @@
       <c r="P86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -16596,7 +16458,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -16746,9 +16608,6 @@
       <c r="P88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -16998,7 +16857,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -17145,9 +17004,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -17293,9 +17149,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -17441,9 +17294,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -17840,9 +17690,6 @@
       <c r="P94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -18092,7 +17939,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -18242,9 +18089,6 @@
       <c r="P96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -18494,7 +18338,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -18644,9 +18488,6 @@
       <c r="P98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -18896,7 +18737,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -19046,9 +18887,6 @@
       <c r="P100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -19298,7 +19136,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -19445,9 +19283,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -19593,9 +19428,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -19744,9 +19576,6 @@
       <c r="P104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -19996,7 +19825,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">

--- a/diseases/d013/2026-2029.xlsx
+++ b/diseases/d013/2026-2029.xlsx
@@ -19900,6 +19900,405 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV106" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA106" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC106" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN107" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV107" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA107" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB107" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC107" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19933,7 +20332,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -20016,7 +20415,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
@@ -20026,7 +20425,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11">
@@ -20046,7 +20445,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d013/2026-2029.xlsx
+++ b/diseases/d013/2026-2029.xlsx
@@ -17105,12 +17105,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -17147,6 +17147,9 @@
         <v>0</v>
       </c>
       <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
@@ -17183,42 +17186,42 @@
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -17250,12 +17253,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -17302,82 +17305,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_POLIO</t>
-        </is>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ92" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_POLIO</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17404,7 +17393,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17453,98 +17442,23 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U93" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_POLIO</t>
         </is>
       </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_POLIO</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X93" t="inlineStr">
-        <is>
-          <t>Polio</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD93" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE93" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF93" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG93" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM polio disease category.</t>
-        </is>
-      </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN93" t="b">
-        <v>1</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -17638,17 +17552,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -17673,7 +17587,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -17687,26 +17601,98 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="P94" t="n">
-        <v>0</v>
-      </c>
-      <c r="R94" t="n">
-        <v>0</v>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_POLIO</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_POLIO</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Polio</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM polio disease category.</t>
+        </is>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN94" t="b">
+        <v>1</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -17725,7 +17711,7 @@
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_POLIO</t>
         </is>
       </c>
       <c r="AT94" t="n">
@@ -17738,42 +17724,42 @@
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -17800,7 +17786,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -17852,98 +17838,23 @@
       <c r="P95" t="n">
         <v>0</v>
       </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U95" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>Acute poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD95" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE95" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF95" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG95" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
-        </is>
-      </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN95" t="b">
-        <v>1</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -18037,7 +17948,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18072,7 +17983,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -18089,23 +18000,98 @@
       <c r="P96" t="n">
         <v>0</v>
       </c>
-      <c r="R96" t="n">
-        <v>0</v>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U96" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN96" t="b">
+        <v>1</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -18199,7 +18185,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18251,98 +18237,23 @@
       <c r="P97" t="n">
         <v>0</v>
       </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U97" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X97" t="inlineStr">
-        <is>
-          <t>Acute poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD97" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE97" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF97" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG97" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN97" t="b">
-        <v>1</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -18436,7 +18347,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18471,7 +18382,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -18488,23 +18399,98 @@
       <c r="P98" t="n">
         <v>0</v>
       </c>
-      <c r="R98" t="n">
-        <v>0</v>
-      </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U98" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN98" t="b">
+        <v>1</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -18598,7 +18584,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -18650,98 +18636,23 @@
       <c r="P99" t="n">
         <v>0</v>
       </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U99" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W99" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>Acute poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD99" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE99" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF99" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG99" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
-        </is>
-      </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN99" t="b">
-        <v>1</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -18835,7 +18746,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -18870,7 +18781,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -18887,23 +18798,98 @@
       <c r="P100" t="n">
         <v>0</v>
       </c>
-      <c r="R100" t="n">
-        <v>0</v>
-      </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U100" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN100" t="b">
+        <v>1</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -18997,7 +18983,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19049,98 +19035,23 @@
       <c r="P101" t="n">
         <v>0</v>
       </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U101" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W101" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Acute poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y101" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD101" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE101" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF101" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG101" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
-        </is>
-      </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN101" t="b">
-        <v>1</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -19234,17 +19145,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -19269,12 +19180,12 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N102" t="n">
@@ -19283,76 +19194,168 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="R102" t="n">
-        <v>0</v>
-      </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN102" t="b">
+        <v>1</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS102" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19384,12 +19387,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -19462,42 +19465,42 @@
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -19529,12 +19532,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -19559,7 +19562,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -19573,9 +19576,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="P104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -19584,82 +19584,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA104" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ104" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -19686,7 +19672,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -19738,98 +19724,23 @@
       <c r="P105" t="n">
         <v>0</v>
       </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U105" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V105" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W105" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t>Acute poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD105" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE105" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF105" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG105" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN105" t="b">
-        <v>1</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -19923,7 +19834,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -19958,7 +19869,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -19975,23 +19886,98 @@
       <c r="P106" t="n">
         <v>0</v>
       </c>
-      <c r="R106" t="n">
-        <v>0</v>
-      </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U106" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN106" t="b">
+        <v>1</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -20085,7 +20071,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -20137,98 +20123,23 @@
       <c r="P107" t="n">
         <v>0</v>
       </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U107" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V107" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W107" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X107" t="inlineStr">
-        <is>
-          <t>Acute poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y107" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD107" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE107" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF107" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG107" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN107" t="b">
-        <v>1</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -20294,6 +20205,243 @@
         </is>
       </c>
       <c r="BC107" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN108" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP108" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV108" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA108" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB108" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC108" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -20415,7 +20563,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -20425,7 +20573,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d013/2026-2029.xlsx
+++ b/diseases/d013/2026-2029.xlsx
@@ -20447,6 +20447,405 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP109" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV109" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA109" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB109" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC109" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN110" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV110" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA110" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB110" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC110" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20480,7 +20879,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -20563,7 +20962,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
@@ -20573,7 +20972,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11">
@@ -20593,7 +20992,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d013/2026-2029.xlsx
+++ b/diseases/d013/2026-2029.xlsx
@@ -1986,7 +1986,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13460,7 +13460,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15229,7 +15229,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16022,7 +16022,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20170,7 +20170,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -20963,7 +20963,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21756,7 +21756,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22549,7 +22549,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24318,7 +24318,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25111,7 +25111,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -25904,7 +25904,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26697,7 +26697,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28321,7 +28321,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -29114,7 +29114,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -29907,7 +29907,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30700,7 +30700,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -31783,7 +31783,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -32576,7 +32576,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -33369,7 +33369,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">

--- a/diseases/d013/2026-2029.xlsx
+++ b/diseases/d013/2026-2029.xlsx
@@ -1986,7 +1986,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13460,7 +13460,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15229,7 +15229,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16022,7 +16022,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20170,7 +20170,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -20963,7 +20963,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21756,7 +21756,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22549,7 +22549,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24318,7 +24318,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25111,7 +25111,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -25904,7 +25904,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26697,7 +26697,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28321,7 +28321,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -29114,7 +29114,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -29907,7 +29907,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30700,7 +30700,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -31783,7 +31783,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -32576,7 +32576,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -33369,7 +33369,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">

--- a/diseases/d013/2026-2029.xlsx
+++ b/diseases/d013/2026-2029.xlsx
@@ -27497,12 +27497,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -27575,42 +27575,42 @@
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -27642,12 +27642,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -27694,82 +27694,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_POLIO</t>
-        </is>
-      </c>
-      <c r="AA145" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ145" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_POLIO</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -27796,7 +27782,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -27845,98 +27831,23 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
+      <c r="R146" t="n">
+        <v>0</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U146" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_POLIO</t>
         </is>
       </c>
-      <c r="V146" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_POLIO</t>
-        </is>
-      </c>
-      <c r="W146" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X146" t="inlineStr">
-        <is>
-          <t>Polio</t>
-        </is>
-      </c>
-      <c r="Y146" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD146" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE146" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF146" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG146" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH146" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK146" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM polio disease category.</t>
-        </is>
-      </c>
-      <c r="AM146" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN146" t="b">
-        <v>1</v>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
@@ -28030,17 +27941,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -28065,7 +27976,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -28079,26 +27990,98 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
-      <c r="P147" t="n">
-        <v>0</v>
-      </c>
-      <c r="R147" t="n">
-        <v>0</v>
-      </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_POLIO</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_POLIO</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>Polio</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM polio disease category.</t>
+        </is>
+      </c>
+      <c r="AM147" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN147" t="b">
+        <v>1</v>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
@@ -28117,7 +28100,7 @@
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_POLIO</t>
         </is>
       </c>
       <c r="AT147" t="n">
@@ -28130,42 +28113,42 @@
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -28192,7 +28175,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -28244,98 +28227,23 @@
       <c r="P148" t="n">
         <v>0</v>
       </c>
+      <c r="R148" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U148" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V148" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W148" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X148" t="inlineStr">
-        <is>
-          <t>Acute poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD148" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE148" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF148" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG148" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH148" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI148" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ148" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK148" t="inlineStr">
-        <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
-        </is>
-      </c>
-      <c r="AM148" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN148" t="b">
-        <v>1</v>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
@@ -28429,17 +28337,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -28481,12 +28389,34 @@
       <c r="P149" t="n">
         <v>0</v>
       </c>
-      <c r="R149" t="n">
-        <v>0</v>
-      </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -28494,6 +28424,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN149" t="b">
+        <v>1</v>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -28501,7 +28489,7 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ149" t="inlineStr">
@@ -28511,55 +28499,55 @@
       </c>
       <c r="AS149" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28586,7 +28574,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -28638,98 +28626,18 @@
       <c r="P150" t="n">
         <v>0</v>
       </c>
-      <c r="U150" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="V150" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="W150" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X150" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y150" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R150" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD150" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE150" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF150" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG150" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI150" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM150" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN150" t="b">
-        <v>1</v>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
@@ -28823,17 +28731,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -28858,7 +28766,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -28875,17 +28783,34 @@
       <c r="P151" t="n">
         <v>0</v>
       </c>
-      <c r="R151" t="n">
-        <v>0</v>
-      </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -28893,6 +28818,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN151" t="b">
+        <v>1</v>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -28900,7 +28883,7 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ151" t="inlineStr">
@@ -28910,55 +28893,55 @@
       </c>
       <c r="AS151" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="AT151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -28985,7 +28968,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -29037,98 +29020,23 @@
       <c r="P152" t="n">
         <v>0</v>
       </c>
+      <c r="R152" t="n">
+        <v>0</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U152" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V152" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W152" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X152" t="inlineStr">
-        <is>
-          <t>Acute poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y152" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD152" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE152" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF152" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG152" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH152" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI152" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
-        </is>
-      </c>
-      <c r="AM152" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN152" t="b">
-        <v>1</v>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
@@ -29222,17 +29130,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -29274,12 +29182,34 @@
       <c r="P153" t="n">
         <v>0</v>
       </c>
-      <c r="R153" t="n">
-        <v>0</v>
-      </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -29287,6 +29217,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM153" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN153" t="b">
+        <v>1</v>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -29294,7 +29282,7 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ153" t="inlineStr">
@@ -29304,55 +29292,55 @@
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29379,7 +29367,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -29431,98 +29419,18 @@
       <c r="P154" t="n">
         <v>0</v>
       </c>
-      <c r="U154" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="V154" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="W154" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X154" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y154" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD154" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE154" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF154" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG154" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ154" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK154" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM154" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN154" t="b">
-        <v>1</v>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
@@ -29616,17 +29524,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -29651,7 +29559,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -29668,17 +29576,34 @@
       <c r="P155" t="n">
         <v>0</v>
       </c>
-      <c r="R155" t="n">
-        <v>0</v>
-      </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -29686,6 +29611,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN155" t="b">
+        <v>1</v>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -29693,7 +29676,7 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ155" t="inlineStr">
@@ -29703,55 +29686,55 @@
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="AT155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -29778,7 +29761,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -29830,98 +29813,23 @@
       <c r="P156" t="n">
         <v>0</v>
       </c>
+      <c r="R156" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U156" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V156" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W156" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X156" t="inlineStr">
-        <is>
-          <t>Acute poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y156" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD156" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE156" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF156" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG156" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN156" t="b">
-        <v>1</v>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
@@ -30015,17 +29923,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -30067,12 +29975,34 @@
       <c r="P157" t="n">
         <v>0</v>
       </c>
-      <c r="R157" t="n">
-        <v>0</v>
-      </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -30080,6 +30010,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN157" t="b">
+        <v>1</v>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -30087,7 +30075,7 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ157" t="inlineStr">
@@ -30097,55 +30085,55 @@
       </c>
       <c r="AS157" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30172,7 +30160,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -30224,98 +30212,18 @@
       <c r="P158" t="n">
         <v>0</v>
       </c>
-      <c r="U158" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="V158" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="W158" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X158" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y158" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD158" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE158" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF158" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG158" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ158" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK158" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM158" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN158" t="b">
-        <v>1</v>
       </c>
       <c r="AO158" t="inlineStr">
         <is>
@@ -30409,17 +30317,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -30444,7 +30352,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -30461,17 +30369,34 @@
       <c r="P159" t="n">
         <v>0</v>
       </c>
-      <c r="R159" t="n">
-        <v>0</v>
-      </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -30479,6 +30404,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN159" t="b">
+        <v>1</v>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -30486,7 +30469,7 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ159" t="inlineStr">
@@ -30496,55 +30479,55 @@
       </c>
       <c r="AS159" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="AT159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -30571,7 +30554,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -30623,98 +30606,23 @@
       <c r="P160" t="n">
         <v>0</v>
       </c>
+      <c r="R160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U160" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V160" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W160" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X160" t="inlineStr">
-        <is>
-          <t>Acute poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y160" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD160" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE160" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF160" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG160" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH160" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI160" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ160" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK160" t="inlineStr">
-        <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
-        </is>
-      </c>
-      <c r="AM160" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN160" t="b">
-        <v>1</v>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
@@ -30808,17 +30716,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -30860,12 +30768,34 @@
       <c r="P161" t="n">
         <v>0</v>
       </c>
-      <c r="R161" t="n">
-        <v>0</v>
-      </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -30873,6 +30803,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN161" t="b">
+        <v>1</v>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -30880,7 +30868,7 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ161" t="inlineStr">
@@ -30890,55 +30878,55 @@
       </c>
       <c r="AS161" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30965,7 +30953,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -31017,98 +31005,18 @@
       <c r="P162" t="n">
         <v>0</v>
       </c>
-      <c r="U162" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="W162" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X162" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y162" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD162" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE162" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF162" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG162" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ162" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK162" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM162" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN162" t="b">
-        <v>1</v>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
@@ -31202,17 +31110,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -31237,12 +31145,12 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N163" t="n">
@@ -31251,76 +31159,168 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="R163" t="n">
-        <v>0</v>
-      </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN163" t="b">
+        <v>1</v>
       </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+        </is>
+      </c>
       <c r="AT163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -31352,12 +31352,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -31430,42 +31430,42 @@
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -31497,12 +31497,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -31527,7 +31527,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -31541,9 +31541,6 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
-      <c r="P165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0</v>
       </c>
@@ -31552,82 +31549,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA165" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ165" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -31654,7 +31637,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -31706,98 +31689,23 @@
       <c r="P166" t="n">
         <v>0</v>
       </c>
+      <c r="R166" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U166" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V166" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W166" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X166" t="inlineStr">
-        <is>
-          <t>Acute poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y166" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD166" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE166" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF166" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG166" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI166" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ166" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK166" t="inlineStr">
-        <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
-        </is>
-      </c>
-      <c r="AM166" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN166" t="b">
-        <v>1</v>
       </c>
       <c r="AO166" t="inlineStr">
         <is>
@@ -31891,17 +31799,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -31943,12 +31851,34 @@
       <c r="P167" t="n">
         <v>0</v>
       </c>
-      <c r="R167" t="n">
-        <v>0</v>
-      </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -31956,6 +31886,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN167" t="b">
+        <v>1</v>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -31963,7 +31951,7 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ167" t="inlineStr">
@@ -31973,55 +31961,55 @@
       </c>
       <c r="AS167" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32048,7 +32036,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -32100,98 +32088,18 @@
       <c r="P168" t="n">
         <v>0</v>
       </c>
-      <c r="U168" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="V168" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="W168" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X168" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y168" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R168" t="n">
+        <v>0</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD168" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE168" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF168" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG168" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH168" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI168" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ168" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK168" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM168" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN168" t="b">
-        <v>1</v>
       </c>
       <c r="AO168" t="inlineStr">
         <is>
@@ -32285,17 +32193,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -32320,7 +32228,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -32337,17 +32245,34 @@
       <c r="P169" t="n">
         <v>0</v>
       </c>
-      <c r="R169" t="n">
-        <v>0</v>
-      </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -32355,6 +32280,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN169" t="b">
+        <v>1</v>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -32362,7 +32345,7 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ169" t="inlineStr">
@@ -32372,55 +32355,55 @@
       </c>
       <c r="AS169" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="AT169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -32447,7 +32430,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -32499,98 +32482,23 @@
       <c r="P170" t="n">
         <v>0</v>
       </c>
+      <c r="R170" t="n">
+        <v>0</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U170" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V170" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W170" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X170" t="inlineStr">
-        <is>
-          <t>Acute poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y170" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD170" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE170" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF170" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG170" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH170" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI170" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ170" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK170" t="inlineStr">
-        <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
-        </is>
-      </c>
-      <c r="AM170" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN170" t="b">
-        <v>1</v>
       </c>
       <c r="AO170" t="inlineStr">
         <is>
@@ -32684,17 +32592,17 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -32736,12 +32644,34 @@
       <c r="P171" t="n">
         <v>0</v>
       </c>
-      <c r="R171" t="n">
-        <v>0</v>
-      </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -32749,6 +32679,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN171" t="b">
+        <v>1</v>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -32756,7 +32744,7 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ171" t="inlineStr">
@@ -32766,55 +32754,55 @@
       </c>
       <c r="AS171" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32841,7 +32829,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -32893,98 +32881,18 @@
       <c r="P172" t="n">
         <v>0</v>
       </c>
-      <c r="U172" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="V172" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="W172" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X172" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y172" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R172" t="n">
+        <v>0</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD172" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE172" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF172" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG172" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH172" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI172" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ172" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK172" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM172" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN172" t="b">
-        <v>1</v>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
@@ -33078,17 +32986,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -33113,7 +33021,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -33130,17 +33038,34 @@
       <c r="P173" t="n">
         <v>0</v>
       </c>
-      <c r="R173" t="n">
-        <v>0</v>
-      </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U173" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -33148,6 +33073,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN173" t="b">
+        <v>1</v>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -33155,7 +33138,7 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ173" t="inlineStr">
@@ -33165,55 +33148,55 @@
       </c>
       <c r="AS173" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="AT173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -33240,7 +33223,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -33292,98 +33275,23 @@
       <c r="P174" t="n">
         <v>0</v>
       </c>
+      <c r="R174" t="n">
+        <v>0</v>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U174" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V174" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W174" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X174" t="inlineStr">
-        <is>
-          <t>Acute poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y174" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD174" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE174" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF174" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG174" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH174" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI174" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ174" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK174" t="inlineStr">
-        <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
-        </is>
-      </c>
-      <c r="AM174" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN174" t="b">
-        <v>1</v>
       </c>
       <c r="AO174" t="inlineStr">
         <is>
@@ -33477,17 +33385,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -33529,12 +33437,34 @@
       <c r="P175" t="n">
         <v>0</v>
       </c>
-      <c r="R175" t="n">
-        <v>0</v>
-      </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -33542,6 +33472,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM175" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN175" t="b">
+        <v>1</v>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -33549,7 +33537,7 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ175" t="inlineStr">
@@ -33559,55 +33547,55 @@
       </c>
       <c r="AS175" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33634,7 +33622,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -33686,98 +33674,18 @@
       <c r="P176" t="n">
         <v>0</v>
       </c>
-      <c r="U176" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="V176" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="W176" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X176" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y176" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R176" t="n">
+        <v>0</v>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD176" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE176" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF176" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG176" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH176" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI176" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ176" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK176" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM176" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN176" t="b">
-        <v>1</v>
       </c>
       <c r="AO176" t="inlineStr">
         <is>
@@ -33843,6 +33751,243 @@
         </is>
       </c>
       <c r="BC176" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" t="n">
+        <v>0</v>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD177" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN177" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP177" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ177" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="AT177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV177" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA177" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB177" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC177" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -33964,7 +34109,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10">
@@ -33974,7 +34119,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d013/2026-2029.xlsx
+++ b/diseases/d013/2026-2029.xlsx
@@ -1986,7 +1986,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13460,7 +13460,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15229,7 +15229,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16022,7 +16022,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20170,7 +20170,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -20963,7 +20963,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21756,7 +21756,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22549,7 +22549,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24318,7 +24318,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25111,7 +25111,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -25904,7 +25904,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26697,7 +26697,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28466,7 +28466,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -29259,7 +29259,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30052,7 +30052,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -30845,7 +30845,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -31928,7 +31928,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -32721,7 +32721,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -33514,7 +33514,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
